--- a/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3868DD89-24CA-4E0E-9EAE-C0C717EA7A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A8D7CA9-81AA-42CA-AFAE-3DC51D16FF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3351,7 +3351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E1942B-ADED-4ABB-B7AA-FB937679E4D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55426B54-6063-4F1E-B584-D9FB04E9BC74}">
   <dimension ref="B2:AF487"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13228,7 +13228,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5013338C-D3F4-4414-B4E2-1F850E2CACA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E0AC4ED-CDB5-4780-AA4B-2B03BF10F5C3}">
   <dimension ref="B9:L60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A8D7CA9-81AA-42CA-AFAE-3DC51D16FF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DEE29CC-7C54-4ADB-BA31-19A603EB7952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3351,7 +3351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55426B54-6063-4F1E-B584-D9FB04E9BC74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C1700D-A113-404F-89CA-60F5425A06C8}">
   <dimension ref="B2:AF487"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13228,7 +13228,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E0AC4ED-CDB5-4780-AA4B-2B03BF10F5C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFA4C15-62CD-43CD-9CD3-72426CE386E0}">
   <dimension ref="B9:L60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
